--- a/qualifiers.xlsx
+++ b/qualifiers.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="5">
   <si>
     <t>Начали</t>
   </si>
@@ -360,10 +360,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -373,8 +373,17 @@
       <c r="D1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -389,8 +398,24 @@
         <f t="shared" ref="D2:D4" si="1">SUM(B2:C2)</f>
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>26</v>
+      </c>
+      <c r="I2">
+        <v>6</v>
+      </c>
+      <c r="J2">
+        <v>32</v>
+      </c>
+      <c r="L2">
+        <f t="shared" ref="L2:L3" si="2">H2 - B2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>4</v>
       </c>
@@ -405,8 +430,24 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -421,8 +462,24 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4">
+        <v>16</v>
+      </c>
+      <c r="L4">
+        <f>H4 - B4</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -437,8 +494,24 @@
         <f>SUM(B5:C5)</f>
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>24</v>
+      </c>
+      <c r="L5">
+        <f t="shared" ref="L5:L6" si="3">H5 - B5</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -452,8 +525,24 @@
         <f>SUM(B6:C6)</f>
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>28</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>28</v>
+      </c>
+      <c r="L6">
+        <f>H6 - B6</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>0</v>
       </c>
@@ -466,8 +555,20 @@
       <c r="E8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H8" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0</v>
       </c>
@@ -479,15 +580,34 @@
         <v>12</v>
       </c>
       <c r="D9">
-        <f t="shared" ref="D9:D10" si="2">D3/2</f>
+        <f t="shared" ref="D9:D10" si="4">D3/2</f>
         <v>6</v>
       </c>
       <c r="E9">
-        <f t="shared" ref="E9:E12" si="3">SUM(B9:D9)</f>
+        <f t="shared" ref="E9:E12" si="5">SUM(B9:D9)</f>
         <v>32</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>14</v>
+      </c>
+      <c r="I9">
+        <v>12</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+      <c r="K9">
+        <v>32</v>
+      </c>
+      <c r="M9">
+        <f>H9 - B9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>4</v>
       </c>
@@ -495,19 +615,38 @@
         <v>6</v>
       </c>
       <c r="C10">
-        <f t="shared" ref="C10:C11" si="4">E11/2</f>
+        <f t="shared" ref="C10:C11" si="6">E11/2</f>
         <v>10</v>
       </c>
       <c r="D10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="E10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10">
+        <v>12</v>
+      </c>
+      <c r="J10">
+        <v>8</v>
+      </c>
+      <c r="K10">
+        <v>24</v>
+      </c>
+      <c r="M10">
+        <f t="shared" ref="M10:M20" si="7">H10 - B10</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>3</v>
       </c>
@@ -515,7 +654,7 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="D11">
@@ -523,11 +662,30 @@
         <v>8</v>
       </c>
       <c r="E11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="I11">
+        <v>6</v>
+      </c>
+      <c r="J11">
+        <v>12</v>
+      </c>
+      <c r="K11">
+        <v>24</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2</v>
       </c>
@@ -542,11 +700,30 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>8</v>
+      </c>
+      <c r="I12">
+        <v>4</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>12</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1</v>
       </c>
@@ -563,8 +740,33 @@
         <f>SUM(B13:D13)</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>8</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M14">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>0</v>
       </c>
@@ -577,8 +779,20 @@
       <c r="E15" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H15" t="s">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
+        <v>3</v>
+      </c>
+      <c r="K15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>0</v>
       </c>
@@ -590,15 +804,34 @@
         <v>20</v>
       </c>
       <c r="D16">
-        <f t="shared" ref="D16:D17" si="5">E10/2</f>
+        <f t="shared" ref="D16:D17" si="8">E10/2</f>
         <v>12</v>
       </c>
       <c r="E16">
-        <f t="shared" ref="E16:E19" si="6">SUM(B16:D16)</f>
+        <f t="shared" ref="E16:E19" si="9">SUM(B16:D16)</f>
         <v>32</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>20</v>
+      </c>
+      <c r="J16">
+        <v>12</v>
+      </c>
+      <c r="K16">
+        <v>32</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>4</v>
       </c>
@@ -606,19 +839,38 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <f t="shared" ref="C17:C18" si="7">E18/2</f>
+        <f t="shared" ref="C17:C18" si="10">E18/2</f>
         <v>20</v>
       </c>
       <c r="D17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="E17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17">
+        <v>8</v>
+      </c>
+      <c r="I17">
+        <v>20</v>
+      </c>
+      <c r="J17">
+        <v>12</v>
+      </c>
+      <c r="K17">
+        <v>40</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="7"/>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>3</v>
       </c>
@@ -626,7 +878,7 @@
         <v>14</v>
       </c>
       <c r="C18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="D18">
@@ -634,11 +886,30 @@
         <v>6</v>
       </c>
       <c r="E18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="H18">
+        <v>12</v>
+      </c>
+      <c r="I18">
+        <v>22</v>
+      </c>
+      <c r="J18">
+        <v>6</v>
+      </c>
+      <c r="K18">
+        <v>40</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="7"/>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2</v>
       </c>
@@ -654,11 +925,30 @@
         <v>12</v>
       </c>
       <c r="E19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>16</v>
+      </c>
+      <c r="I19">
+        <v>10</v>
+      </c>
+      <c r="J19">
+        <v>18</v>
+      </c>
+      <c r="K19">
+        <v>44</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="7"/>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1</v>
       </c>
@@ -675,8 +965,27 @@
         <f>SUM(B20:D20)</f>
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>20</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>20</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
@@ -684,6 +993,12 @@
       <c r="C22">
         <f xml:space="preserve"> SUM(B2:B20) - 166</f>
         <v>0</v>
+      </c>
+      <c r="G22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
